--- a/viewer/downloads/Grade_6_MN2022_Alignment.xlsx
+++ b/viewer/downloads/Grade_6_MN2022_Alignment.xlsx
@@ -487,7 +487,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>CC1 11.1.1 ()</t>
+          <t>CC1 11.1.1 (); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>CC1 11.1.1 ()</t>
+          <t>CC1 11.1.1 (); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.1.3 ()</t>
+          <t>CC1 10.1.3 (); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.1.3 (); CC1 8.1.4 (How can I display variability?); CC1 9.1.1 (Volume is a measure of cubic u); CC1 9.2.2 (Benchmark Percents can be used)</t>
+          <t>CC1 10.1.3 (); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids); CC1 8.1.4 (How can I display variability?); CC1 9.1.1 (Volume is a measure of cubic u); CC1 9.2.2 (Benchmark Percents can be used)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>CC1 1.1.2 (Area and Perimeter); CC1 2.1.1 (Analyzing Data); CC1 6.3.1 ()</t>
+          <t>CC1 1.1.2 (Area and Perimeter); CC1 2.1.1 (Analyzing Data); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids); CC1 6.3.1 ()</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.3.2 ()</t>
+          <t>CC1 10.3.2 (); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.4.2 ()</t>
+          <t>CC1 10.4.2 (); CC1 2.2.1 (Area of Polygons); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>CC1 3.2.4 (Positioning Integers in the Co)</t>
+          <t>CC1 2.2.1 (Area of Polygons); CC1 3.2.4 (Positioning Integers in the Co); CC1 5.3.1 (Decompose shapes into rectangl); CC1 5.3.2 (Area of Parallelogram); CC1 5.3.3 (Area of Triangles); CC1 5.3.4 (Area of Trapezoids)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.1.3 (); CC1 9.1.1 (Volume is a measure of cubic u)</t>
+          <t>CC1 10.1.3 (); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.4 (Understanding the Distributive); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC1 9.1.1 (Volume is a measure of cubic u); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>CC1 11.2.2 (); CC1 3.1.2 (Expressing Portions as Percent); CC1 3.1.3 (Connecting Percents with Decim); CC1 6.2.1 (Order of Operations); CC1 7.1.1 (Compare using rates)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 11.2.2 (); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.3 (Defining Greatest Common Facto); CC1 2.3.4 (Understanding the Distributive); CC1 3.1.2 (Expressing Portions as Percent); CC1 3.1.3 (Connecting Percents with Decim); CC1 3.1.4 (Representing Portions in Multi); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 6.2.1 (Order of Operations); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.1 (Compare using rates); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC1 9.2.3 (Use percent knowledge to calcu); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>CC1 3.1.6 (Ratios); CC1 3.2.1 (Adding and Subtracting Integer); CC1 3.2.2 (Ordering Rational Numbers); CC1 3.2.4 (Positioning Integers in the Co)</t>
+          <t>CC1 3.1.6 (Ratios); CC1 3.2.1 (Adding and Subtracting Integer); CC1 3.2.2 (Ordering Rational Numbers); CC1 3.2.4 (Positioning Integers in the Co); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>CC1 3.2.2 (Ordering Rational Numbers); CC1 3.2.3 (Absolute Value and Zero)</t>
+          <t>CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.4 (Understanding the Distributive); CC1 3.2.2 (Ordering Rational Numbers); CC1 3.2.3 (Absolute Value and Zero); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>CC1 1.2.4 (Number Sense)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 1.2.4 (Number Sense); CC1 2.3.3 (Defining Greatest Common Facto); CC1 3.1.4 (Representing Portions in Multi); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>CC1 2.2.3 (Area and Perimeter); CC1 3.1.1 (Using the Multiplicative Ident); CC1 3.2.2 (Ordering Rational Numbers)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 2.2.3 (Area and Perimeter); CC1 2.3.3 (Defining Greatest Common Facto); CC1 3.1.1 (Using the Multiplicative Ident); CC1 3.1.4 (Representing Portions in Multi); CC1 3.2.2 (Ordering Rational Numbers); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>CC1 3.2.3 (Absolute Value and Zero); CC1 3.2.4 (Positioning Integers in the Co)</t>
+          <t>CC1 3.2.3 (Absolute Value and Zero); CC1 3.2.4 (Positioning Integers in the Co); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>CC1 6.1.4 (Section Closure); CC1 8.1.2 (Compare data sets using histog); CC1 9.2.1 (Ratios can be represented as p); CC1 9.2.2 (Benchmark Percents can be used)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 2.3.3 (Defining Greatest Common Facto); CC1 3.1.4 (Representing Portions in Multi); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 6.1.4 (Section Closure); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC1 8.1.2 (Compare data sets using histog); CC1 9.2.1 (Ratios can be represented as p); CC1 9.2.2 (Benchmark Percents can be used)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>CC1 8.1.2 (Compare data sets using histog); CC1 8.1.4 (How can I display variability?); CC1 9.2.1 (Ratios can be represented as p); CC1 9.2.4 (Use percent knowledge to calcu)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 2.3.3 (Defining Greatest Common Facto); CC1 3.1.4 (Representing Portions in Multi); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC1 8.1.2 (Compare data sets using histog); CC1 8.1.4 (How can I display variability?); CC1 9.2.1 (Ratios can be represented as p); CC1 9.2.4 (Use percent knowledge to calcu)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>CC1 8.1.1 (Mean and Median measure the ce); CC1 8.2.1 (Statistical Questions); CC1 9.1.1 (Volume is a measure of cubic u); CC1 9.1.2 (Surface Area is the area of al); CC1 9.2.1 (Ratios can be represented as p); CC1 9.2.4 (Use percent knowledge to calcu)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.3 (Defining Greatest Common Facto); CC1 2.3.4 (Understanding the Distributive); CC1 3.1.4 (Representing Portions in Multi); CC1 4.1.2 (Writing Equivalent Expressions); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC1 8.1.1 (Mean and Median measure the ce); CC1 8.2.1 (Statistical Questions); CC1 9.1.1 (Volume is a measure of cubic u); CC1 9.1.2 (Surface Area is the area of al); CC1 9.2.1 (Ratios can be represented as p); CC1 9.2.4 (Use percent knowledge to calcu)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>CC1 2.2.2 (Area  of Rectangles); CC1 8.2.1 (Statistical Questions); CC1 9.3.2 (); CC1 9.3.3 ()</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 2.2.2 (Area  of Rectangles); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.3 (Defining Greatest Common Facto); CC1 2.3.4 (Understanding the Distributive); CC1 3.1.4 (Representing Portions in Multi); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC1 8.2.1 (Statistical Questions); CC1 9.3.2 (); CC1 9.3.3 (); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>CC1 3.1.3 (Connecting Percents with Decim); CC1 3.1.5 (Representing Portions in Multi)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.3 (Defining Greatest Common Facto); CC1 2.3.4 (Understanding the Distributive); CC1 3.1.3 (Connecting Percents with Decim); CC1 3.1.4 (Representing Portions in Multi); CC1 3.1.5 (Representing Portions in Multi); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC1 9.2.3 (Use percent knowledge to calcu); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.1.3 (); CC1 5.1.1 (Representing Fraction Multipli); CC1 5.1.3 (Connection Diagrams to Algorit); CC1 9.3.1 ()</t>
+          <t>CC1 10.1.3 (); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.4 (Understanding the Distributive); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.1.1 (Representing Fraction Multipli); CC1 5.1.3 (Connection Diagrams to Algorit); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC1 9.3.1 (); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.1.3 (); CC1 5.1.1 (Representing Fraction Multipli); CC1 5.1.3 (Connection Diagrams to Algorit); CC1 9.3.1 ()</t>
+          <t>CC1 10.1.3 (); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.4 (Understanding the Distributive); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.1.1 (Representing Fraction Multipli); CC1 5.1.3 (Connection Diagrams to Algorit); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC1 9.3.1 (); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>CC1 3.1.6 (Ratios); CC1 5.2.1 (Multiplying Decimals)</t>
+          <t>CC1 3.1.6 (Ratios); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.2.1 (Multiplying Decimals); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.4 (Fraction Division as Ratios); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>CC1 11.2.2 (); CC1 3.1.2 (Expressing Portions as Percent); CC1 6.2.1 (Order of Operations)</t>
+          <t>CC1 1.2.1 (); CC1 1.2.2 (); CC1 1.2.3 (Number Sense); CC1 11.2.2 (); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.3 (Defining Greatest Common Facto); CC1 2.3.4 (Understanding the Distributive); CC1 3.1.2 (Expressing Portions as Percent); CC1 3.1.4 (Representing Portions in Multi); CC1 4.1.2 (Writing Equivalent Expressions); CC1 4.2.1 (Using Scale Factor for Enlarge); CC1 4.2.2 (Using Scale Factor for Enlarge); CC1 4.2.3 (Using Ratios to Compare Simila); CC1 4.2.4 (Using Ratios that Apply to Dif); CC1 5.1.2 (Representing Fraction Multipli); CC1 5.1.4 (Multiplying Mixed Numbers); CC1 5.2.2 (Fraction Multiplication Number); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.1.2 (Consider meanings of numbers i); CC1 6.1.3 (Dividing by unit fractions is ); CC1 6.2.1 (Order of Operations); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 7.1.2 (Compare using tables and graph); CC1 7.1.3 (Compare using unit rates); CC1 7.2.1 (Model fraction division); CC1 7.2.2 (Alternate Strategies for fract); CC1 7.2.3 (Fraction Division Algorithm); CC1 7.2.4 (Fraction Division as Ratios); CC2 1.2.4 (Percent)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>CC1 10.1.3 (); CC1 5.1.1 (Representing Fraction Multipli); CC1 5.1.3 (Connection Diagrams to Algorit); CC1 9.3.1 (); CC1 9.3.2 ()</t>
+          <t>CC1 10.1.3 (); CC1 2.3.1 (Multiplying Multi-Digit Number); CC1 2.3.2 (Multiplying Multi-Digit Number); CC1 2.3.4 (Understanding the Distributive); CC1 4.1.2 (Writing Equivalent Expressions); CC1 5.1.1 (Representing Fraction Multipli); CC1 5.1.3 (Connection Diagrams to Algorit); CC1 6.1.1 (Quotients can be expressed as ); CC1 6.2.2 (Algebra Tiles); CC1 6.2.3 (Algebra Tiles); CC1 6.2.4 (Combining Like Terms); CC1 6.2.5 (Evaluate expressions); CC1 9.3.1 (); CC1 9.3.2 ()</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
